--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/126.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/126.xlsx
@@ -426,13 +426,13 @@
         <v>-14.65429856444998</v>
       </c>
       <c r="E2">
-        <v>-11.13300635849475</v>
+        <v>-22.4350948027803</v>
       </c>
       <c r="F2">
-        <v>-1.71051173626886</v>
+        <v>-4.364861830570358</v>
       </c>
       <c r="G2">
-        <v>-7.187980652842007</v>
+        <v>-15.34093357946264</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.98172937811257</v>
       </c>
       <c r="E3">
-        <v>-10.6198668547896</v>
+        <v>-21.79066578064477</v>
       </c>
       <c r="F3">
-        <v>-1.942907726022053</v>
+        <v>-4.769613740721836</v>
       </c>
       <c r="G3">
-        <v>-6.82969094588</v>
+        <v>-14.53963466548454</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.28643847535087</v>
       </c>
       <c r="E4">
-        <v>-11.68768102579826</v>
+        <v>-21.52639309450514</v>
       </c>
       <c r="F4">
-        <v>-1.866079134514607</v>
+        <v>-4.584510902729272</v>
       </c>
       <c r="G4">
-        <v>-7.114766756186117</v>
+        <v>-14.75414124371168</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.6283712779376</v>
       </c>
       <c r="E5">
-        <v>-12.96186681428449</v>
+        <v>-21.39869465596284</v>
       </c>
       <c r="F5">
-        <v>-1.72293062037163</v>
+        <v>-4.400533816037113</v>
       </c>
       <c r="G5">
-        <v>-6.875480392742052</v>
+        <v>-14.5110371789832</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.00587560282842</v>
       </c>
       <c r="E6">
-        <v>-13.56601958859581</v>
+        <v>-22.56711340552592</v>
       </c>
       <c r="F6">
-        <v>-1.558322420291729</v>
+        <v>-4.308468234522573</v>
       </c>
       <c r="G6">
-        <v>-6.906504342586602</v>
+        <v>-14.04956453825212</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.43183954952928</v>
       </c>
       <c r="E7">
-        <v>-13.66791025376839</v>
+        <v>-22.53123430596314</v>
       </c>
       <c r="F7">
-        <v>-1.505716948376947</v>
+        <v>-3.504927831152372</v>
       </c>
       <c r="G7">
-        <v>-6.706166079053145</v>
+        <v>-13.04399645731235</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.89759992412603</v>
       </c>
       <c r="E8">
-        <v>-14.49747687875952</v>
+        <v>-22.70659946191018</v>
       </c>
       <c r="F8">
-        <v>-1.355539736821216</v>
+        <v>-3.680492018501699</v>
       </c>
       <c r="G8">
-        <v>-6.056674521133539</v>
+        <v>-12.56441311418391</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.39712480907189</v>
       </c>
       <c r="E9">
-        <v>-14.9351810624449</v>
+        <v>-25.7116223578161</v>
       </c>
       <c r="F9">
-        <v>-1.037827703151494</v>
+        <v>-3.876033942504342</v>
       </c>
       <c r="G9">
-        <v>-5.782928768872186</v>
+        <v>-12.08659834947601</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.924298933489572</v>
       </c>
       <c r="E10">
-        <v>-16.25202960455739</v>
+        <v>-24.14481110742823</v>
       </c>
       <c r="F10">
-        <v>-1.013453820691521</v>
+        <v>-3.965127341777637</v>
       </c>
       <c r="G10">
-        <v>-5.454271773813524</v>
+        <v>-11.61979864554317</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.474024991658284</v>
       </c>
       <c r="E11">
-        <v>-16.74773901180702</v>
+        <v>-26.57415627358307</v>
       </c>
       <c r="F11">
-        <v>-1.254960195140703</v>
+        <v>-3.40731384477388</v>
       </c>
       <c r="G11">
-        <v>-5.021409744470017</v>
+        <v>-13.09056027246243</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.039142169081902</v>
       </c>
       <c r="E12">
-        <v>-16.75460870687666</v>
+        <v>-28.34729385670842</v>
       </c>
       <c r="F12">
-        <v>-1.137181261075863</v>
+        <v>-3.115296111204193</v>
       </c>
       <c r="G12">
-        <v>-4.33895503476423</v>
+        <v>-11.10236969294809</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.612249362065542</v>
       </c>
       <c r="E13">
-        <v>-17.29097022529315</v>
+        <v>-26.94400127426352</v>
       </c>
       <c r="F13">
-        <v>-1.127258247957728</v>
+        <v>-3.015376778343711</v>
       </c>
       <c r="G13">
-        <v>-3.782978291288799</v>
+        <v>-10.73415429076876</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.201403547926612</v>
       </c>
       <c r="E14">
-        <v>-18.61376465377771</v>
+        <v>-27.30209488489406</v>
       </c>
       <c r="F14">
-        <v>-0.8568095448221343</v>
+        <v>-3.020279885000881</v>
       </c>
       <c r="G14">
-        <v>-3.368317197935532</v>
+        <v>-10.31313419003329</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.810373626600297</v>
       </c>
       <c r="E15">
-        <v>-19.33908127863825</v>
+        <v>-27.74759710082065</v>
       </c>
       <c r="F15">
-        <v>-0.7368056159133756</v>
+        <v>-3.071202114353176</v>
       </c>
       <c r="G15">
-        <v>-2.527340112249852</v>
+        <v>-9.151306135378871</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.440236688473939</v>
       </c>
       <c r="E16">
-        <v>-20.43266246675057</v>
+        <v>-28.20420313501405</v>
       </c>
       <c r="F16">
-        <v>-0.2703511030295712</v>
+        <v>-2.881173803783566</v>
       </c>
       <c r="G16">
-        <v>-2.140165811900054</v>
+        <v>-8.607213976391749</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.086644612783665</v>
       </c>
       <c r="E17">
-        <v>-21.005591412779</v>
+        <v>-29.49194491044224</v>
       </c>
       <c r="F17">
-        <v>-0.2003880205565278</v>
+        <v>-2.732570490293154</v>
       </c>
       <c r="G17">
-        <v>-1.999401406999875</v>
+        <v>-9.187114106257091</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.753192742643467</v>
       </c>
       <c r="E18">
-        <v>-21.87309306453238</v>
+        <v>-30.12160657883876</v>
       </c>
       <c r="F18">
-        <v>-0.4716468670120595</v>
+        <v>-2.901726427414425</v>
       </c>
       <c r="G18">
-        <v>-1.74811889753448</v>
+        <v>-8.586913058603464</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.439906527538515</v>
       </c>
       <c r="E19">
-        <v>-23.10675806759797</v>
+        <v>-33.14539547103247</v>
       </c>
       <c r="F19">
-        <v>-0.1957582751422813</v>
+        <v>-1.782131553547503</v>
       </c>
       <c r="G19">
-        <v>-1.617043939899342</v>
+        <v>-9.365054751425779</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.145097049087191</v>
       </c>
       <c r="E20">
-        <v>-23.29633810345508</v>
+        <v>-32.07101274847568</v>
       </c>
       <c r="F20">
-        <v>-0.1107818618608996</v>
+        <v>-2.659335356579053</v>
       </c>
       <c r="G20">
-        <v>-0.9357573450687167</v>
+        <v>-8.853856838572089</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.864095405950315</v>
       </c>
       <c r="E21">
-        <v>-23.67520835283281</v>
+        <v>-32.73781696068312</v>
       </c>
       <c r="F21">
-        <v>0.1839595437291925</v>
+        <v>-2.498376114908484</v>
       </c>
       <c r="G21">
-        <v>-0.6564138288269503</v>
+        <v>-7.64561918618088</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.5979028030577</v>
       </c>
       <c r="E22">
-        <v>-24.12628059178884</v>
+        <v>-33.55587899745775</v>
       </c>
       <c r="F22">
-        <v>-0.05073847903638027</v>
+        <v>-2.787992411377455</v>
       </c>
       <c r="G22">
-        <v>0.6212019722171576</v>
+        <v>-7.93912445467321</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.347764671076747</v>
       </c>
       <c r="E23">
-        <v>-24.32516211325771</v>
+        <v>-32.99152471696285</v>
       </c>
       <c r="F23">
-        <v>0.2279524797570686</v>
+        <v>-2.980538130484172</v>
       </c>
       <c r="G23">
-        <v>0.2017568578302207</v>
+        <v>-7.221892077658868</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.114240310171634</v>
       </c>
       <c r="E24">
-        <v>-25.08308375097348</v>
+        <v>-34.56809709307426</v>
       </c>
       <c r="F24">
-        <v>0.2254922285707541</v>
+        <v>-2.552990377775055</v>
       </c>
       <c r="G24">
-        <v>0.5923403473802819</v>
+        <v>-6.661843338228166</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.895608253616882</v>
       </c>
       <c r="E25">
-        <v>-25.46487486608616</v>
+        <v>-33.16311765406149</v>
       </c>
       <c r="F25">
-        <v>0.5114769623458526</v>
+        <v>-2.53452192652964</v>
       </c>
       <c r="G25">
-        <v>0.8462478340932329</v>
+        <v>-7.046458285761597</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.691673945046974</v>
       </c>
       <c r="E26">
-        <v>-25.43134604453337</v>
+        <v>-35.03452085891629</v>
       </c>
       <c r="F26">
-        <v>0.5994396401143265</v>
+        <v>-2.627555869538053</v>
       </c>
       <c r="G26">
-        <v>0.5746972190551476</v>
+        <v>-6.079127920264819</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.5037258694591</v>
       </c>
       <c r="E27">
-        <v>-25.25314606385754</v>
+        <v>-34.22655052646774</v>
       </c>
       <c r="F27">
-        <v>0.4193558802153252</v>
+        <v>-2.236525865413949</v>
       </c>
       <c r="G27">
-        <v>0.1806290722089562</v>
+        <v>-6.475515890753538</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.332665107191417</v>
       </c>
       <c r="E28">
-        <v>-25.66145592275913</v>
+        <v>-35.47238353919195</v>
       </c>
       <c r="F28">
-        <v>0.252686702037259</v>
+        <v>-2.715341276682328</v>
       </c>
       <c r="G28">
-        <v>0.6119817396351179</v>
+        <v>-7.488005708572953</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.178896486404226</v>
       </c>
       <c r="E29">
-        <v>-25.3260997801211</v>
+        <v>-33.68416840185805</v>
       </c>
       <c r="F29">
-        <v>0.5112640719233331</v>
+        <v>-2.316820346134708</v>
       </c>
       <c r="G29">
-        <v>0.03397159338801514</v>
+        <v>-7.342171816363433</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.043957828647271</v>
       </c>
       <c r="E30">
-        <v>-25.57958564117446</v>
+        <v>-33.5478794481232</v>
       </c>
       <c r="F30">
-        <v>0.6298498358384992</v>
+        <v>-2.567635913456551</v>
       </c>
       <c r="G30">
-        <v>0.4642545825857979</v>
+        <v>-7.24173690565039</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.932473312887721</v>
       </c>
       <c r="E31">
-        <v>-25.31544428078105</v>
+        <v>-33.28558344088793</v>
       </c>
       <c r="F31">
-        <v>0.4451918311412389</v>
+        <v>-2.691698014271624</v>
       </c>
       <c r="G31">
-        <v>-0.4968381807264754</v>
+        <v>-6.794106098067823</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.849516244666912</v>
       </c>
       <c r="E32">
-        <v>-23.4233391570002</v>
+        <v>-31.24919207827467</v>
       </c>
       <c r="F32">
-        <v>0.1721064345625343</v>
+        <v>-2.510731214721238</v>
       </c>
       <c r="G32">
-        <v>-0.1372983283503207</v>
+        <v>-8.050853329993862</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.797790337822126</v>
       </c>
       <c r="E33">
-        <v>-23.68005834849503</v>
+        <v>-33.86037585397052</v>
       </c>
       <c r="F33">
-        <v>0.1982397693860531</v>
+        <v>-2.201306168549122</v>
       </c>
       <c r="G33">
-        <v>-0.4265445712584913</v>
+        <v>-7.57607041400689</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.776945256077201</v>
       </c>
       <c r="E34">
-        <v>-23.31710115678025</v>
+        <v>-32.00590008495639</v>
       </c>
       <c r="F34">
-        <v>0.6699527585428288</v>
+        <v>-2.707042692041082</v>
       </c>
       <c r="G34">
-        <v>-0.9482620804317605</v>
+        <v>-7.4872575900574</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.787737320617909</v>
       </c>
       <c r="E35">
-        <v>-23.33173265629903</v>
+        <v>-32.25907574554022</v>
       </c>
       <c r="F35">
-        <v>0.3926675392319307</v>
+        <v>-2.723149467821116</v>
       </c>
       <c r="G35">
-        <v>-0.8253934579167936</v>
+        <v>-8.52311626782318</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.832122024123513</v>
       </c>
       <c r="E36">
-        <v>-22.77819463597145</v>
+        <v>-30.55058665734837</v>
       </c>
       <c r="F36">
-        <v>0.07403436101029526</v>
+        <v>-2.821578567723961</v>
       </c>
       <c r="G36">
-        <v>-0.9265863308100687</v>
+        <v>-8.916042549566685</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.911278262120625</v>
       </c>
       <c r="E37">
-        <v>-21.89384706090953</v>
+        <v>-30.2815658662117</v>
       </c>
       <c r="F37">
-        <v>0.4504411953727794</v>
+        <v>-2.259800504330407</v>
       </c>
       <c r="G37">
-        <v>-0.7876200353244661</v>
+        <v>-10.38137703602663</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.025300963101816</v>
       </c>
       <c r="E38">
-        <v>-21.87928348850086</v>
+        <v>-28.56886756142972</v>
       </c>
       <c r="F38">
-        <v>0.2980712953018383</v>
+        <v>-2.568933965176738</v>
       </c>
       <c r="G38">
-        <v>-1.282490589698359</v>
+        <v>-8.314597918942029</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.174891490441189</v>
       </c>
       <c r="E39">
-        <v>-20.53689888145913</v>
+        <v>-28.77540220397155</v>
       </c>
       <c r="F39">
-        <v>0.5136737926980769</v>
+        <v>-2.931710842293558</v>
       </c>
       <c r="G39">
-        <v>-1.801658589719939</v>
+        <v>-8.108973607476306</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.36212712855663</v>
       </c>
       <c r="E40">
-        <v>-20.50681622862617</v>
+        <v>-29.53707115392867</v>
       </c>
       <c r="F40">
-        <v>0.4077545947391181</v>
+        <v>-2.425363812025735</v>
       </c>
       <c r="G40">
-        <v>-1.595325534397377</v>
+        <v>-8.647674719441261</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.589422496007775</v>
       </c>
       <c r="E41">
-        <v>-19.58450192748395</v>
+        <v>-27.35571201714487</v>
       </c>
       <c r="F41">
-        <v>0.598652691081667</v>
+        <v>-2.155875186709986</v>
       </c>
       <c r="G41">
-        <v>-2.117600851235752</v>
+        <v>-8.290051100455823</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.856285458705177</v>
       </c>
       <c r="E42">
-        <v>-19.27705477015519</v>
+        <v>-27.87974250083848</v>
       </c>
       <c r="F42">
-        <v>0.5229639331204733</v>
+        <v>-1.944701969816517</v>
       </c>
       <c r="G42">
-        <v>-1.462455748569223</v>
+        <v>-8.117832905686807</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.159987530855057</v>
       </c>
       <c r="E43">
-        <v>-18.76980681113401</v>
+        <v>-26.49365811962272</v>
       </c>
       <c r="F43">
-        <v>0.7967493001545435</v>
+        <v>-2.82646345029827</v>
       </c>
       <c r="G43">
-        <v>-2.181223737273385</v>
+        <v>-8.417323122303564</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.496759410244216</v>
       </c>
       <c r="E44">
-        <v>-17.40821694582575</v>
+        <v>-26.95138268689602</v>
       </c>
       <c r="F44">
-        <v>0.813146004525557</v>
+        <v>-2.660490100738556</v>
       </c>
       <c r="G44">
-        <v>-1.638647502646726</v>
+        <v>-10.60530728257249</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.865417860863503</v>
       </c>
       <c r="E45">
-        <v>-16.38679699102566</v>
+        <v>-26.34539135213759</v>
       </c>
       <c r="F45">
-        <v>0.6025277937919631</v>
+        <v>-1.583599223220753</v>
       </c>
       <c r="G45">
-        <v>-1.871223768001727</v>
+        <v>-9.381693825953723</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.260981089794597</v>
       </c>
       <c r="E46">
-        <v>-16.10038912393654</v>
+        <v>-26.26454450567865</v>
       </c>
       <c r="F46">
-        <v>0.7858049100287564</v>
+        <v>-2.15015945163067</v>
       </c>
       <c r="G46">
-        <v>-1.960295808454413</v>
+        <v>-10.1386650772745</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.675626901913758</v>
       </c>
       <c r="E47">
-        <v>-15.57454725063986</v>
+        <v>-25.2293308190512</v>
       </c>
       <c r="F47">
-        <v>0.7360117454464782</v>
+        <v>-1.624043433295036</v>
       </c>
       <c r="G47">
-        <v>-2.742191218740732</v>
+        <v>-10.65872228833869</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.098540305133988</v>
       </c>
       <c r="E48">
-        <v>-14.80765017744089</v>
+        <v>-25.44624472401861</v>
       </c>
       <c r="F48">
-        <v>0.8018172519248709</v>
+        <v>-1.970955417913441</v>
       </c>
       <c r="G48">
-        <v>-2.74882256751237</v>
+        <v>-9.521234335212228</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.524779465334213</v>
       </c>
       <c r="E49">
-        <v>-13.38894266947387</v>
+        <v>-23.78073085415955</v>
       </c>
       <c r="F49">
-        <v>0.8521322879709129</v>
+        <v>-2.340905956738506</v>
       </c>
       <c r="G49">
-        <v>-2.864019694021355</v>
+        <v>-11.49816048111299</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.945658369999828</v>
       </c>
       <c r="E50">
-        <v>-13.78322331589971</v>
+        <v>-23.63938812343214</v>
       </c>
       <c r="F50">
-        <v>0.9691574076992047</v>
+        <v>-1.56139400662131</v>
       </c>
       <c r="G50">
-        <v>-2.51866128122512</v>
+        <v>-10.29305311408949</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.351151425280449</v>
       </c>
       <c r="E51">
-        <v>-13.12582021573219</v>
+        <v>-20.93768241655998</v>
       </c>
       <c r="F51">
-        <v>1.012025420794079</v>
+        <v>-2.294412179521578</v>
       </c>
       <c r="G51">
-        <v>-3.22485562891349</v>
+        <v>-11.07163777182233</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.729264075478314</v>
       </c>
       <c r="E52">
-        <v>-12.76712431805863</v>
+        <v>-21.09158260571065</v>
       </c>
       <c r="F52">
-        <v>0.9532593805046765</v>
+        <v>-1.613357493798923</v>
       </c>
       <c r="G52">
-        <v>-2.867835754694989</v>
+        <v>-10.76882695898742</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.078014655894089</v>
       </c>
       <c r="E53">
-        <v>-11.73293859503092</v>
+        <v>-20.21403227013425</v>
       </c>
       <c r="F53">
-        <v>0.9768744784236848</v>
+        <v>-1.65819702131246</v>
       </c>
       <c r="G53">
-        <v>-2.736478612005739</v>
+        <v>-11.16450290439774</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.39307851210466</v>
       </c>
       <c r="E54">
-        <v>-10.69176543660938</v>
+        <v>-20.55824610793128</v>
       </c>
       <c r="F54">
-        <v>1.124656879817922</v>
+        <v>-1.759232165064513</v>
       </c>
       <c r="G54">
-        <v>-3.292173170427058</v>
+        <v>-10.36941370222089</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.668784414963422</v>
       </c>
       <c r="E55">
-        <v>-10.35391410479312</v>
+        <v>-20.56812723821602</v>
       </c>
       <c r="F55">
-        <v>0.9301131385356527</v>
+        <v>-2.104479131203291</v>
       </c>
       <c r="G55">
-        <v>-4.211689575359608</v>
+        <v>-11.23133482512051</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.900176683356248</v>
       </c>
       <c r="E56">
-        <v>-10.44105553012272</v>
+        <v>-20.3902895354608</v>
       </c>
       <c r="F56">
-        <v>0.8100760749307819</v>
+        <v>-2.214122669005236</v>
       </c>
       <c r="G56">
-        <v>-3.552275603444241</v>
+        <v>-11.84238687247122</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.08961770667247</v>
       </c>
       <c r="E57">
-        <v>-10.60442475842344</v>
+        <v>-19.23051564277836</v>
       </c>
       <c r="F57">
-        <v>0.9724891013932643</v>
+        <v>-2.125692792021583</v>
       </c>
       <c r="G57">
-        <v>-4.285103626530623</v>
+        <v>-11.3578095101293</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.23900691734362</v>
       </c>
       <c r="E58">
-        <v>-8.912233648185195</v>
+        <v>-17.9217685406656</v>
       </c>
       <c r="F58">
-        <v>0.830465510183289</v>
+        <v>-2.966539549744263</v>
       </c>
       <c r="G58">
-        <v>-4.449105642514789</v>
+        <v>-11.76087148526993</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.34805694967237</v>
       </c>
       <c r="E59">
-        <v>-8.120171844925595</v>
+        <v>-19.11813703180402</v>
       </c>
       <c r="F59">
-        <v>0.9789901287704348</v>
+        <v>-2.079319128078061</v>
       </c>
       <c r="G59">
-        <v>-4.542482645653467</v>
+        <v>-13.25492322281813</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.4183019390892</v>
       </c>
       <c r="E60">
-        <v>-8.362725969724435</v>
+        <v>-17.88405088065571</v>
       </c>
       <c r="F60">
-        <v>0.6883441716197835</v>
+        <v>-1.799382304710802</v>
       </c>
       <c r="G60">
-        <v>-4.493671193735167</v>
+        <v>-11.84412591989772</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.45393731115439</v>
       </c>
       <c r="E61">
-        <v>-8.218213307191659</v>
+        <v>-17.93583850940743</v>
       </c>
       <c r="F61">
-        <v>0.7684970015146636</v>
+        <v>-1.766584754131761</v>
       </c>
       <c r="G61">
-        <v>-4.839718663058886</v>
+        <v>-13.42148459161866</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.4597479428615</v>
       </c>
       <c r="E62">
-        <v>-7.809509471051395</v>
+        <v>-18.55986675613842</v>
       </c>
       <c r="F62">
-        <v>0.54875929404365</v>
+        <v>-2.19569232266035</v>
       </c>
       <c r="G62">
-        <v>-4.659363038822447</v>
+        <v>-12.13650901061672</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.43608132674428</v>
       </c>
       <c r="E63">
-        <v>-7.43184832423371</v>
+        <v>-19.53542232618882</v>
       </c>
       <c r="F63">
-        <v>0.683140367595397</v>
+        <v>-2.849609692267294</v>
       </c>
       <c r="G63">
-        <v>-5.323944934693939</v>
+        <v>-11.98446704721673</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.3846051313156</v>
       </c>
       <c r="E64">
-        <v>-7.491207561526252</v>
+        <v>-17.13702022292839</v>
       </c>
       <c r="F64">
-        <v>0.7898142082583061</v>
+        <v>-3.168222989671262</v>
       </c>
       <c r="G64">
-        <v>-5.460634062417287</v>
+        <v>-13.16709476533648</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.30818838936301</v>
       </c>
       <c r="E65">
-        <v>-6.82453014659103</v>
+        <v>-17.48673615664474</v>
       </c>
       <c r="F65">
-        <v>0.5913042438514325</v>
+        <v>-3.062399882331028</v>
       </c>
       <c r="G65">
-        <v>-5.539734470550822</v>
+        <v>-12.77453269918607</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.21125319851024</v>
       </c>
       <c r="E66">
-        <v>-7.417782883965885</v>
+        <v>-18.54949655066085</v>
       </c>
       <c r="F66">
-        <v>0.4681773698341196</v>
+        <v>-2.540757876337915</v>
       </c>
       <c r="G66">
-        <v>-5.496130317247361</v>
+        <v>-11.67412911212445</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.09403248121946</v>
       </c>
       <c r="E67">
-        <v>-7.361942270977302</v>
+        <v>-17.28953922750673</v>
       </c>
       <c r="F67">
-        <v>0.110001245272447</v>
+        <v>-2.48389376760534</v>
       </c>
       <c r="G67">
-        <v>-4.954456418549548</v>
+        <v>-12.85298670667239</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.956603246323882</v>
       </c>
       <c r="E68">
-        <v>-6.452094858778197</v>
+        <v>-14.88754604435822</v>
       </c>
       <c r="F68">
-        <v>0.4672893599783186</v>
+        <v>-2.781889828721031</v>
       </c>
       <c r="G68">
-        <v>-5.061617833459453</v>
+        <v>-12.56433108364492</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.801409509406096</v>
       </c>
       <c r="E69">
-        <v>-6.97140667255581</v>
+        <v>-18.07481284822883</v>
       </c>
       <c r="F69">
-        <v>0.3328958609155296</v>
+        <v>-2.444636608019269</v>
       </c>
       <c r="G69">
-        <v>-5.019769133690295</v>
+        <v>-12.51996896816123</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.631994432065074</v>
       </c>
       <c r="E70">
-        <v>-6.71456521226277</v>
+        <v>-15.78567829429948</v>
       </c>
       <c r="F70">
-        <v>0.09764531709228957</v>
+        <v>-2.723943043792997</v>
       </c>
       <c r="G70">
-        <v>-5.108431021448051</v>
+        <v>-12.08602413570311</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.448156577082798</v>
       </c>
       <c r="E71">
-        <v>-7.558238033787789</v>
+        <v>-15.71870216372603</v>
       </c>
       <c r="F71">
-        <v>0.2476974451701976</v>
+        <v>-3.502975369183973</v>
       </c>
       <c r="G71">
-        <v>-5.222499407740587</v>
+        <v>-11.7708496800322</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.246722482285625</v>
       </c>
       <c r="E72">
-        <v>-7.322050943443734</v>
+        <v>-18.69066267090196</v>
       </c>
       <c r="F72">
-        <v>-0.1664605768400684</v>
+        <v>-2.995186151267876</v>
       </c>
       <c r="G72">
-        <v>-5.046438902525463</v>
+        <v>-12.28705801820717</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.030133070478231</v>
       </c>
       <c r="E73">
-        <v>-8.425196268660248</v>
+        <v>-16.81318904663988</v>
       </c>
       <c r="F73">
-        <v>0.2473967478029814</v>
+        <v>-3.192007074540442</v>
       </c>
       <c r="G73">
-        <v>-4.097480096540015</v>
+        <v>-11.76235787863636</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.801031010832649</v>
       </c>
       <c r="E74">
-        <v>-7.868945692402067</v>
+        <v>-17.78595960517557</v>
       </c>
       <c r="F74">
-        <v>-0.121237515219035</v>
+        <v>-2.972365457688153</v>
       </c>
       <c r="G74">
-        <v>-4.485179392339324</v>
+        <v>-12.33079670159456</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.559537513828008</v>
       </c>
       <c r="E75">
-        <v>-7.886380317331598</v>
+        <v>-18.8216940663139</v>
       </c>
       <c r="F75">
-        <v>-0.08506768094319739</v>
+        <v>-3.346137255342331</v>
       </c>
       <c r="G75">
-        <v>-4.394384710567929</v>
+        <v>-10.09473280181509</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.302439451695545</v>
       </c>
       <c r="E76">
-        <v>-8.143801422297621</v>
+        <v>-18.79668330436954</v>
       </c>
       <c r="F76">
-        <v>-0.03794103103053071</v>
+        <v>-2.692410410238032</v>
       </c>
       <c r="G76">
-        <v>-4.71436287460186</v>
+        <v>-10.14488955457277</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.034476870945776</v>
       </c>
       <c r="E77">
-        <v>-8.88763497737553</v>
+        <v>-17.94230517029039</v>
       </c>
       <c r="F77">
-        <v>-0.02566628285584763</v>
+        <v>-2.85175682057535</v>
       </c>
       <c r="G77">
-        <v>-3.41979956420322</v>
+        <v>-10.47049173235958</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.759337121418664</v>
       </c>
       <c r="E78">
-        <v>-9.933286796590661</v>
+        <v>-18.65227026826493</v>
       </c>
       <c r="F78">
-        <v>-0.07740445409989916</v>
+        <v>-3.458096080035101</v>
       </c>
       <c r="G78">
-        <v>-3.249878224525816</v>
+        <v>-11.5662753594655</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.479718598478106</v>
       </c>
       <c r="E79">
-        <v>-9.513470085235573</v>
+        <v>-18.45046788106112</v>
       </c>
       <c r="F79">
-        <v>-0.329967048274246</v>
+        <v>-3.021929992867258</v>
       </c>
       <c r="G79">
-        <v>-3.19212216263647</v>
+        <v>-9.845832459201857</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.195354608123919</v>
       </c>
       <c r="E80">
-        <v>-10.49839053953384</v>
+        <v>-20.09222084780193</v>
       </c>
       <c r="F80">
-        <v>-0.4031549650463879</v>
+        <v>-2.468408267377406</v>
       </c>
       <c r="G80">
-        <v>-2.426734578015717</v>
+        <v>-11.00366398599687</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.911673535698344</v>
       </c>
       <c r="E81">
-        <v>-11.15568948479917</v>
+        <v>-20.11498095816448</v>
       </c>
       <c r="F81">
-        <v>-0.1272290966434838</v>
+        <v>-2.807452418404021</v>
       </c>
       <c r="G81">
-        <v>-2.295091969050795</v>
+        <v>-9.566754721906404</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.633833356059839</v>
       </c>
       <c r="E82">
-        <v>-12.09256282987606</v>
+        <v>-21.41420920791312</v>
       </c>
       <c r="F82">
-        <v>0.05385450271069651</v>
+        <v>-3.065453244577747</v>
       </c>
       <c r="G82">
-        <v>-1.734367297978847</v>
+        <v>-9.177966060549361</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.366287719579447</v>
       </c>
       <c r="E83">
-        <v>-13.45753093679405</v>
+        <v>-23.09015668188585</v>
       </c>
       <c r="F83">
-        <v>-0.3113296100786599</v>
+        <v>-3.732050434019343</v>
       </c>
       <c r="G83">
-        <v>-1.799965479395266</v>
+        <v>-9.612393232576721</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.11086714060491</v>
       </c>
       <c r="E84">
-        <v>-13.39709845116169</v>
+        <v>-22.90660857340696</v>
       </c>
       <c r="F84">
-        <v>-0.1904434698859197</v>
+        <v>-3.452729087632363</v>
       </c>
       <c r="G84">
-        <v>-1.350779372793522</v>
+        <v>-8.444970695163445</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.872051198495399</v>
       </c>
       <c r="E85">
-        <v>-15.40981042318883</v>
+        <v>-25.90596634832929</v>
       </c>
       <c r="F85">
-        <v>-0.4999728903507886</v>
+        <v>-2.783471182092976</v>
       </c>
       <c r="G85">
-        <v>-1.238495971029324</v>
+        <v>-7.145114774389421</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.654975993044586</v>
       </c>
       <c r="E86">
-        <v>-15.75699493993489</v>
+        <v>-25.4911128444866</v>
       </c>
       <c r="F86">
-        <v>-0.2683224312601152</v>
+        <v>-2.490162023742324</v>
       </c>
       <c r="G86">
-        <v>-0.7516611282545115</v>
+        <v>-6.405054938986022</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.463714703537958</v>
       </c>
       <c r="E87">
-        <v>-17.27352654341561</v>
+        <v>-25.91753659941888</v>
       </c>
       <c r="F87">
-        <v>-0.4179272409405115</v>
+        <v>-3.11106978071511</v>
       </c>
       <c r="G87">
-        <v>-0.6354861977208118</v>
+        <v>-7.61104823583057</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.2992974714426</v>
       </c>
       <c r="E88">
-        <v>-19.2534433066792</v>
+        <v>-27.67229763502111</v>
       </c>
       <c r="F88">
-        <v>-0.4471346471958193</v>
+        <v>-3.041709749711305</v>
       </c>
       <c r="G88">
-        <v>-0.04196243594065447</v>
+        <v>-6.524100938384236</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.16228467016106</v>
       </c>
       <c r="E89">
-        <v>-20.60486674784025</v>
+        <v>-29.53649377349269</v>
       </c>
       <c r="F89">
-        <v>-0.5865513661891845</v>
+        <v>-2.998463172713351</v>
       </c>
       <c r="G89">
-        <v>-0.0915023190451508</v>
+        <v>-8.141369107932704</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.054663850521274</v>
       </c>
       <c r="E90">
-        <v>-22.24383470306634</v>
+        <v>-29.11314938088563</v>
       </c>
       <c r="F90">
-        <v>-0.5033783087436974</v>
+        <v>-2.644469475168413</v>
       </c>
       <c r="G90">
-        <v>-0.01246753534280592</v>
+        <v>-7.588831084651571</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.978000577302453</v>
       </c>
       <c r="E91">
-        <v>-23.77705373326532</v>
+        <v>-31.05418466631937</v>
       </c>
       <c r="F91">
-        <v>-0.7674717771650134</v>
+        <v>-2.728719410237539</v>
       </c>
       <c r="G91">
-        <v>0.6094650426990238</v>
+        <v>-8.023576535170198</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.931272175177089</v>
       </c>
       <c r="E92">
-        <v>-25.65750709342444</v>
+        <v>-33.14736309298881</v>
       </c>
       <c r="F92">
-        <v>-0.7227838408861884</v>
+        <v>-3.627423489208751</v>
       </c>
       <c r="G92">
-        <v>0.4663151897251292</v>
+        <v>-7.80510624129925</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.910609149110006</v>
       </c>
       <c r="E93">
-        <v>-27.72419847562302</v>
+        <v>-34.46723891997542</v>
       </c>
       <c r="F93">
-        <v>-0.8298693801482888</v>
+        <v>-3.012975341242996</v>
       </c>
       <c r="G93">
-        <v>0.3488507391185678</v>
+        <v>-6.961484491036657</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.914413419729222</v>
       </c>
       <c r="E94">
-        <v>-29.13366789661439</v>
+        <v>-36.91978798694556</v>
       </c>
       <c r="F94">
-        <v>-1.17876281959419</v>
+        <v>-3.659730646285335</v>
       </c>
       <c r="G94">
-        <v>0.2314387880569576</v>
+        <v>-6.947601642618647</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.940685880177142</v>
       </c>
       <c r="E95">
-        <v>-31.21099892849398</v>
+        <v>-37.97569453555106</v>
       </c>
       <c r="F95">
-        <v>-1.168421480937641</v>
+        <v>-3.682813932331746</v>
       </c>
       <c r="G95">
-        <v>-0.2370966820808317</v>
+        <v>-6.229824582825437</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.98516834961134</v>
       </c>
       <c r="E96">
-        <v>-33.61320721415786</v>
+        <v>-37.87312459927733</v>
       </c>
       <c r="F96">
-        <v>-1.322911173192346</v>
+        <v>-3.985432283555058</v>
       </c>
       <c r="G96">
-        <v>-0.1156291411717478</v>
+        <v>-7.203251457979663</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.038933372607953</v>
       </c>
       <c r="E97">
-        <v>-35.94690195232268</v>
+        <v>-42.11766102242976</v>
       </c>
       <c r="F97">
-        <v>-1.653689874273828</v>
+        <v>-3.529398632598472</v>
       </c>
       <c r="G97">
-        <v>-0.5878887977795069</v>
+        <v>-7.991788060702298</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.098626712144302</v>
       </c>
       <c r="E98">
-        <v>-37.81732247831781</v>
+        <v>-41.66257429126593</v>
       </c>
       <c r="F98">
-        <v>-1.381364918970893</v>
+        <v>-3.65180814044496</v>
       </c>
       <c r="G98">
-        <v>-0.7617147911126501</v>
+        <v>-7.376890421683918</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.156247596666836</v>
       </c>
       <c r="E99">
-        <v>-40.03142701065108</v>
+        <v>-45.05046834333536</v>
       </c>
       <c r="F99">
-        <v>-1.822061347464647</v>
+        <v>-4.393500976787346</v>
       </c>
       <c r="G99">
-        <v>-1.127856461266407</v>
+        <v>-7.922843033295245</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.211932740153525</v>
       </c>
       <c r="E100">
-        <v>-42.5305423758421</v>
+        <v>-47.70787425322749</v>
       </c>
       <c r="F100">
-        <v>-2.362990231697141</v>
+        <v>-3.980480303221123</v>
       </c>
       <c r="G100">
-        <v>-1.905847217896987</v>
+        <v>-9.753968099202082</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.25236496534801</v>
       </c>
       <c r="E101">
-        <v>-44.8087270796209</v>
+        <v>-47.92162049062654</v>
       </c>
       <c r="F101">
-        <v>-2.119880137956139</v>
+        <v>-4.548387457027991</v>
       </c>
       <c r="G101">
-        <v>-1.70072821455142</v>
+        <v>-9.434468993515832</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.28912234245469</v>
       </c>
       <c r="E102">
-        <v>-47.41109844489781</v>
+        <v>-51.00662303021893</v>
       </c>
       <c r="F102">
-        <v>-2.196626721090708</v>
+        <v>-5.080932434776751</v>
       </c>
       <c r="G102">
-        <v>-2.035225783985893</v>
+        <v>-9.871238957736637</v>
       </c>
     </row>
   </sheetData>
